--- a/AC_2014/3-Karimnagar_7_032.xlsx
+++ b/AC_2014/3-Karimnagar_7_032.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -106,11 +111,33 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +172,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -4085,7 +4121,7 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="D56" s="6" t="n">
         <v>0</v>
@@ -4124,7 +4160,7 @@
         <v>7</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>2674</v>
+        <v>298</v>
       </c>
       <c r="Q56" s="6" t="n">
         <v>0</v>
@@ -4133,7 +4169,7 @@
         <v>2</v>
       </c>
       <c r="S56" s="6" t="n">
-        <v>2676</v>
+        <v>300</v>
       </c>
       <c r="T56" s="6" t="n">
         <v>0</v>
@@ -14023,7 +14059,7 @@
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>4145</v>
+        <v>0</v>
       </c>
       <c r="D202" s="6" t="n">
         <v>0</v>
@@ -14062,7 +14098,7 @@
         <v>24</v>
       </c>
       <c r="P202" s="6" t="n">
-        <v>4576</v>
+        <v>431</v>
       </c>
       <c r="Q202" s="6" t="n">
         <v>0</v>
@@ -14071,7 +14107,7 @@
         <v>0</v>
       </c>
       <c r="S202" s="6" t="n">
-        <v>4576</v>
+        <v>431</v>
       </c>
       <c r="T202" s="6" t="n">
         <v>0</v>
@@ -20333,235 +20369,236 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="7" t="inlineStr">
+      <c r="A295" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B295" s="8" t="inlineStr"/>
-      <c r="C295" s="9">
+      <c r="B295" s="11" t="inlineStr"/>
+      <c r="C295" s="19">
         <f>SUM(C6:C294)</f>
         <v/>
       </c>
-      <c r="D295" s="9">
+      <c r="D295" s="19">
         <f>SUM(D6:D294)</f>
         <v/>
       </c>
-      <c r="E295" s="9">
+      <c r="E295" s="19">
         <f>SUM(E6:E294)</f>
         <v/>
       </c>
-      <c r="F295" s="9">
+      <c r="F295" s="19">
         <f>SUM(F6:F294)</f>
         <v/>
       </c>
-      <c r="G295" s="9">
+      <c r="G295" s="19">
         <f>SUM(G6:G294)</f>
         <v/>
       </c>
-      <c r="H295" s="9">
+      <c r="H295" s="19">
         <f>SUM(H6:H294)</f>
         <v/>
       </c>
-      <c r="I295" s="9">
+      <c r="I295" s="19">
         <f>SUM(I6:I294)</f>
         <v/>
       </c>
-      <c r="J295" s="9">
+      <c r="J295" s="19">
         <f>SUM(J6:J294)</f>
         <v/>
       </c>
-      <c r="K295" s="9">
+      <c r="K295" s="19">
         <f>SUM(K6:K294)</f>
         <v/>
       </c>
-      <c r="L295" s="9">
+      <c r="L295" s="19">
         <f>SUM(L6:L294)</f>
         <v/>
       </c>
-      <c r="M295" s="9">
+      <c r="M295" s="19">
         <f>SUM(M6:M294)</f>
         <v/>
       </c>
-      <c r="N295" s="9">
+      <c r="N295" s="19">
         <f>SUM(N6:N294)</f>
         <v/>
       </c>
-      <c r="O295" s="9">
+      <c r="O295" s="19">
         <f>SUM(O6:O294)</f>
         <v/>
       </c>
-      <c r="P295" s="9">
+      <c r="P295" s="19">
         <f>SUM(P6:P294)</f>
         <v/>
       </c>
-      <c r="Q295" s="9">
+      <c r="Q295" s="19">
         <f>SUM(Q6:Q294)</f>
         <v/>
       </c>
-      <c r="R295" s="9">
+      <c r="R295" s="19">
         <f>SUM(R6:R294)</f>
         <v/>
       </c>
-      <c r="S295" s="9">
+      <c r="S295" s="19">
         <f>SUM(S6:S294)</f>
         <v/>
       </c>
-      <c r="T295" s="9">
+      <c r="T295" s="19">
         <f>SUM(T6:T294)</f>
         <v/>
       </c>
-      <c r="U295" s="9">
+      <c r="U295" s="19">
         <f>SUM(U6:U294)</f>
         <v/>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="10" t="inlineStr">
+      <c r="A296" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B296" s="11" t="inlineStr"/>
-      <c r="C296" s="12" t="n">
+      <c r="C296" s="19" t="n">
         <v>434</v>
       </c>
-      <c r="D296" s="12" t="n">
+      <c r="D296" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="E296" s="12" t="n">
+      <c r="E296" s="19" t="n">
         <v>408</v>
       </c>
-      <c r="F296" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G296" s="12" t="n">
+      <c r="F296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H296" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I296" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J296" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K296" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L296" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M296" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N296" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O296" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P296" s="12" t="n">
+      <c r="H296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" s="19" t="n">
         <v>850</v>
       </c>
-      <c r="Q296" s="12" t="n">
+      <c r="Q296" s="19" t="n">
         <v>102</v>
       </c>
-      <c r="R296" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S296" s="12" t="n">
+      <c r="R296" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S296" s="19" t="n">
         <v>953</v>
       </c>
-      <c r="T296" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U296" s="13" t="n">
+      <c r="T296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U296" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="14" t="inlineStr">
+      <c r="A297" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B297" s="15" t="inlineStr"/>
-      <c r="C297" s="16">
+      <c r="B297" s="11" t="inlineStr"/>
+      <c r="C297" s="20">
         <f>C295+C296</f>
         <v/>
       </c>
-      <c r="D297" s="16">
+      <c r="D297" s="20">
         <f>D295+D296</f>
         <v/>
       </c>
-      <c r="E297" s="16">
+      <c r="E297" s="20">
         <f>E295+E296</f>
         <v/>
       </c>
-      <c r="F297" s="16">
+      <c r="F297" s="20">
         <f>F295+F296</f>
         <v/>
       </c>
-      <c r="G297" s="16">
+      <c r="G297" s="20">
         <f>G295+G296</f>
         <v/>
       </c>
-      <c r="H297" s="16">
+      <c r="H297" s="20">
         <f>H295+H296</f>
         <v/>
       </c>
-      <c r="I297" s="16">
+      <c r="I297" s="20">
         <f>I295+I296</f>
         <v/>
       </c>
-      <c r="J297" s="16">
+      <c r="J297" s="20">
         <f>J295+J296</f>
         <v/>
       </c>
-      <c r="K297" s="16">
+      <c r="K297" s="20">
         <f>K295+K296</f>
         <v/>
       </c>
-      <c r="L297" s="16">
+      <c r="L297" s="20">
         <f>L295+L296</f>
         <v/>
       </c>
-      <c r="M297" s="16">
+      <c r="M297" s="20">
         <f>M295+M296</f>
         <v/>
       </c>
-      <c r="N297" s="16">
+      <c r="N297" s="20">
         <f>N295+N296</f>
         <v/>
       </c>
-      <c r="O297" s="16">
+      <c r="O297" s="20">
         <f>O295+O296</f>
         <v/>
       </c>
-      <c r="P297" s="16">
+      <c r="P297" s="20">
         <f>P295+P296</f>
         <v/>
       </c>
-      <c r="Q297" s="16">
+      <c r="Q297" s="20">
         <f>Q295+Q296</f>
         <v/>
       </c>
-      <c r="R297" s="16">
+      <c r="R297" s="20">
         <f>R295+R296</f>
         <v/>
       </c>
-      <c r="S297" s="16">
+      <c r="S297" s="20">
         <f>S295+S296</f>
         <v/>
       </c>
-      <c r="T297" s="16">
+      <c r="T297" s="20">
         <f>T295+T296</f>
         <v/>
       </c>
-      <c r="U297" s="17" t="n">
-        <v>0</v>
+      <c r="U297" s="20">
+        <f>U295+U296</f>
+        <v/>
       </c>
     </row>
   </sheetData>
